--- a/data/trans_orig/IQ11_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ11_1-Estudios-trans_orig.xlsx
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>26651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45560</t>
+          <t>45133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>52039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>34497</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>65520</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>27454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32641</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45224</t>
+          <t>45525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57701</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -5438,12 +5438,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>21929</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5888,12 +5888,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>74886</t>
+          <t>74844</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6195,12 +6195,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>29530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38473</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45529</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -8392,12 +8392,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>37549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>25099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10689,12 +10689,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11872,12 +11872,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11887,12 +11887,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39565</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ11_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ11_1-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1054,72 +1054,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>674</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -1165,74 +1165,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3440</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>83,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>34,63%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1278,57 +1278,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>4114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1615,84 +1615,84 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1178</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3742</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1178</t>
-        </is>
-      </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1726,72 +1726,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2858</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6528</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>537</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2759</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3133</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2858</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6480</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -1837,74 +1837,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30202</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26458</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32426</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>19196</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16974</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16600</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>19733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>84,12%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30202</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>26651</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>32366</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>77,84%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>75</t>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45133</t>
+          <t>45043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52039</t>
+          <t>52073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -1950,57 +1950,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>34237</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>34237</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>34237</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>19733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>19733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>19733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>34237</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>34237</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>34237</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2065,84 +2065,84 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>660</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -2398,84 +2398,84 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>614</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>614</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>40,39%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -2509,72 +2509,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5490</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2815</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>81,16%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>41,62%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>9351</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>5490</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3250</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>81,16%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2622,57 +2622,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>9351</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>9351</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>9351</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2737,84 +2737,84 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>660</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2959,84 +2959,84 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>1178</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>3863</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1178</t>
-        </is>
-      </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3070,107 +3070,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3472</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7633</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3815</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3739</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>3,65%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>4682</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>8850</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>11,49%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3472</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7596</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>17,33%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>4682</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>9035</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -3181,74 +3181,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>38531</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>34164</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>41299</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>77,93%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>31987</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>29383</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>29459</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>33198</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>96,35%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>88,51%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>88,74%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>38531</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>34497</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>41314</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>87,89%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>78,69%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>106</t>
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65520</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73812</t>
+          <t>73671</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -3294,57 +3294,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>43841</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>43841</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>43841</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>33198</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>33198</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>33198</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>43841</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>43841</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>43841</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3474,7 +3474,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3640,84 +3640,84 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3358</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>28,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -3867,59 +3867,59 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3904</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,78%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3333</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>31,22%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>82,24%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3365</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -3978,59 +3978,59 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3252</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>66,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -4084,72 +4084,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9387</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6055</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11259</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2132</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4053</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3471</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>52,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9387</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6552</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11325</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,81%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -4197,57 +4197,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11911</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11911</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>11911</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>4053</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>4053</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>4053</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>11911</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>11911</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>11911</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4312,72 +4312,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1302</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4246</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -4423,64 +4423,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3052</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1452</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4470</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4441</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>4,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3381</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -4534,72 +4534,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5054</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9317</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1499</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5216</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,43%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5054</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9406</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -4645,72 +4645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8516</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6378</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2981</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10995</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10759</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4052</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1435</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8107</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -4756,72 +4756,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28595</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23781</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32779</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23226</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18260</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27454</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18840</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27372</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28595</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23457</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>32504</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45525</t>
+          <t>45300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57837</t>
+          <t>57605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -4869,57 +4869,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>33857</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>33857</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>33857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38376</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38376</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38376</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5211,59 +5211,59 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>1462</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4335</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4406</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>16,21%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>48,1%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3971</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -5322,59 +5322,59 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,09%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>769</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3807</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3592</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>8,53%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5428,72 +5428,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12481</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9613</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13887</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>86,13%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>66,33%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>95,82%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>6784</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3967</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9014</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3821</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8325</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>75,26%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>12481</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>9703</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>13969</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>86,13%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21929</t>
+          <t>22016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -5541,57 +5541,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14492</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>14492</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14492</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>9014</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>9014</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>9014</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>14492</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>14492</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>14492</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5656,64 +5656,64 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1302</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3243</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -5767,64 +5767,64 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3505</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>1452</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4397</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5147</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3377</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5878,72 +5878,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7544</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12990</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>4226</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>8624</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>8899</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>9,01%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>7544</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>12857</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5456</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10259</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>7802</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>4230</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>12831</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4176</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>12805</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>27,35%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2629</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>10308</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19948</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -6100,72 +6100,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>50463</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>44737</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>55188</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>69,06%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>85,2%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>32141</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>26211</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>36979</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>26009</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>36811</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>68,5%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>55,86%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>78,81%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>50463</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>44629</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>55352</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>77,9%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>74844</t>
+          <t>74550</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>89354</t>
+          <t>89341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6195,12 +6195,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -6213,57 +6213,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>64778</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>64778</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>64778</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>46923</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>46923</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>46923</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>64778</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>64778</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>64778</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6382,7 +6382,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6393,7 +6393,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7008,42 +7008,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>2457</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7121,52 +7121,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2457</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7342,72 +7342,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3061</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3242</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>3,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -7453,84 +7453,84 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3939</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -7564,72 +7564,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2762</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6464</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>601</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3062</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2873</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2762</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6537</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -7675,74 +7675,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27366</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23222</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29585</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>15282</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12783</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12639</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>76,6%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27366</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23326</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29530</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>61</t>
@@ -7755,12 +7755,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>45470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -7788,57 +7788,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30841</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30841</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30841</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>16500</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>30841</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>30841</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30841</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8014,84 +8014,84 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>51,3%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -8125,84 +8125,84 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -8236,79 +8236,79 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2664</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
           <t>634</t>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -8352,67 +8352,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>4759</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>69,93%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>31,2%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>4759</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6161</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>69,93%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -8460,57 +8460,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>4412</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8691,59 +8691,59 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3531</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3476</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -8797,84 +8797,84 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>1426</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5162</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -8908,72 +8908,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1198</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7511</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>601</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3153</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2485</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3396</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7517</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -9019,74 +9019,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>34654</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>29463</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>37541</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>86,26%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>22151</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>19704</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>19676</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>94,79%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>34654</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>30199</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>37549</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>86,26%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>75,17%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>93,46%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>83</t>
@@ -9099,12 +9099,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51947</t>
+          <t>51235</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59855</t>
+          <t>59935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -9132,57 +9132,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>40176</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>40176</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>40176</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>23369</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>40176</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>40176</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>40176</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9301,7 +9301,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -9312,7 +9312,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -9922,64 +9922,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -10035,57 +10035,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10110,17 +10110,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10372,72 +10372,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3276</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,73%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>634</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>946</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>735</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -10594,74 +10594,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12783</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9794</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>71,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9590</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6730</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9623</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6847</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10992</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>62,29%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>13785</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10481</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14746</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>71,07%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>33</t>
@@ -10669,32 +10669,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>22405</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19438</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25099</t>
+          <t>24455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -10707,57 +10707,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10782,17 +10782,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11155,82 +11155,82 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5224</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>26,49%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>65,82%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -11271,34 +11271,34 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>70,64%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -11306,32 +11306,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11341,27 +11341,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11379,57 +11379,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11454,17 +11454,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11716,72 +11716,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3475</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>20,26%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>634</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -11827,72 +11827,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8321</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3989</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>23,26%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>735</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11902,22 +11902,22 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -11938,74 +11938,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>19138</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>13930</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>21582</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>62,6%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>15722</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>12895</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>15815</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>12906</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>17184</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>75,1%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>20971</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>15427</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>23407</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>87,26%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>64,19%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>50</t>
@@ -12013,32 +12013,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30400</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39565</t>
+          <t>37874</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -12051,57 +12051,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12126,17 +12126,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
